--- a/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
@@ -632,14 +632,13 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -656,13 +655,14 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -698,12 +698,13 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">30226
 </t>
         </is>
       </c>
@@ -715,7 +716,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -727,13 +728,14 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -750,7 +752,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -774,7 +776,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">623
 </t>
         </is>
       </c>
@@ -786,7 +788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -798,7 +800,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -816,7 +818,8 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -833,8 +836,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -845,19 +847,19 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -875,19 +877,18 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>616</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -904,8 +905,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">4316
 </t>
         </is>
       </c>
@@ -952,13 +952,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -968,10 +968,16 @@
 </t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">606
+</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -982,7 +988,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -1000,7 +1006,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1030,7 +1036,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -1054,12 +1060,12 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1089,12 +1095,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -1106,8 +1112,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1124,31 +1129,31 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">060
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1502
+</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">173
 </t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1173
-</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8726
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -1160,7 +1165,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">3189
 </t>
         </is>
       </c>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -1190,30 +1195,30 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -1231,26 +1236,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2972
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>526</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1261,13 +1262,13 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1278,8 +1279,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">18656
 </t>
         </is>
       </c>
@@ -1302,13 +1302,13 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1350,25 +1350,25 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1385,42 +1385,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66631</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925
-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">925
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">601
-</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1431,19 +1426,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">443
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -1461,7 +1454,8 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1477,7 +1471,8 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t xml:space="preserve">319
+</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -1500,18 +1495,19 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">024
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1535,8 +1531,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333
-</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1547,7 +1542,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1558,14 +1553,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1576,11 +1569,15 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5447
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -1589,13 +1586,13 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1613,8 +1610,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -1625,31 +1621,29 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1661,7 +1655,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">8065
 </t>
         </is>
       </c>
@@ -1685,19 +1679,18 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450
+          <t xml:space="preserve">4456
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
@@ -1709,7 +1702,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
@@ -1721,13 +1714,13 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1748,7 +1741,12 @@
 </t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">879
@@ -1769,7 +1767,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -1781,7 +1779,8 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t xml:space="preserve">850
+</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1804,13 +1803,13 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2309
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -1846,8 +1845,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1858,8 +1856,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1900,7 +1897,8 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1911,19 +1909,19 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">2722
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -1941,19 +1939,17 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -1971,7 +1967,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -1989,8 +1985,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2567
-</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2019,7 +2014,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2037,7 +2032,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -2055,14 +2050,13 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2073,7 +2067,7 @@
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">4286
 </t>
         </is>
       </c>
@@ -2085,7 +2079,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">3247
 </t>
         </is>
       </c>
@@ -2103,14 +2097,13 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
@@ -2121,8 +2114,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2145,7 +2137,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">3408
 </t>
         </is>
       </c>
@@ -2157,7 +2149,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2169,13 +2161,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2193,25 +2185,25 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -2235,13 +2227,13 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2277,7 +2269,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2306,20 +2298,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>418</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2348,25 +2337,24 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -2414,7 +2402,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -2426,19 +2414,18 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -2456,19 +2443,19 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19928
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">9291
 </t>
         </is>
       </c>
@@ -2510,26 +2497,31 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
+          <t xml:space="preserve">1609
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9186
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211222
+</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2540,12 +2532,14 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t xml:space="preserve">425
+</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2556,8 +2550,7 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2568,23 +2561,24 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>464</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -2602,7 +2596,9 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t xml:space="preserve">1
+3986
+</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2619,32 +2615,28 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
@@ -2662,7 +2654,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2686,50 +2678,57 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">2428
+</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2744,35 +2743,36 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1373
+          <t xml:space="preserve">432
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2783,13 +2783,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2801,7 +2800,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -2813,13 +2812,13 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2429
 </t>
         </is>
       </c>
@@ -2831,7 +2830,8 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">231
+</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2842,12 +2842,13 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>044</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2870,13 +2871,14 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">46
+8 179
 </t>
         </is>
       </c>
@@ -2918,20 +2920,19 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2942,8 +2943,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2954,13 +2954,13 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3008,8 +3008,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -3020,18 +3019,21 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">212
+44
+</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">62
+818
 </t>
         </is>
       </c>
@@ -3049,40 +3051,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568
-</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t xml:space="preserve">235
+</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">3
+1 8 4
+7
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -3094,13 +3098,12 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -3118,20 +3121,17 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -3148,14 +3148,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -3166,23 +3164,21 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="2" t="n"/>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
           <t>13</t>
@@ -3203,8 +3199,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3219,14 +3214,10 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3244,7 +3235,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -3256,7 +3247,8 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3285,19 +3277,19 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">417
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">5310
 </t>
         </is>
       </c>
@@ -3309,23 +3301,25 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t xml:space="preserve">259
+8111
+</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3346,24 +3340,82 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">340
+</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="n"/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8720
+</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">26
@@ -3390,8 +3442,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -3402,25 +3453,24 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -3444,87 +3494,142 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
-</t>
+          <t>19855</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492
+</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8826
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">965
+</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4382
+</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1462
+</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29526
+</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">854
+</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">21
 </t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n"/>
-      <c r="Q23" s="2" t="n"/>
-      <c r="R23" s="2" t="n"/>
-      <c r="S23" s="2" t="n"/>
-      <c r="T23" s="2" t="n"/>
-      <c r="U23" s="2" t="n"/>
-      <c r="V23" s="2" t="n"/>
-      <c r="W23" s="2" t="n"/>
-      <c r="X23" s="2" t="n"/>
-      <c r="Y23" s="2" t="n"/>
-      <c r="Z23" s="2" t="n"/>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3539,139 +3644,137 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19255
-</t>
+          <t>58511</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">603
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">492
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4372
+          <t xml:space="preserve">8724
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t xml:space="preserve">590
+</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -3687,141 +3790,65 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3851
-</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">306
-</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>8161</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">874
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="n"/>
+      <c r="R25" s="2" t="n"/>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590
-</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="n"/>
+      <c r="U25" s="2" t="n"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="X25" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="inlineStr">
-        <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="n"/>
+      <c r="X25" s="2" t="n"/>
+      <c r="Y25" s="2" t="n"/>
+      <c r="Z25" s="2" t="n"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3836,48 +3863,53 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">3261
+</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -3889,13 +3921,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2604
 </t>
         </is>
       </c>
@@ -3907,19 +3938,19 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3930,8 +3961,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3942,7 +3972,8 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3953,8 +3984,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3965,7 +3995,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3983,8 +4013,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
-</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -4001,26 +4030,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -4037,7 +4072,8 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -4048,19 +4084,19 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -4078,25 +4114,24 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -4114,7 +4149,8 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">16
+54
 </t>
         </is>
       </c>
@@ -4132,17 +4168,19 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">284
+</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -4153,24 +4191,25 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4182,31 +4221,30 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4224,48 +4262,47 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">684
+</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">684
-</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>081</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4288,14 +4325,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -4312,58 +4347,58 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12396
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
 </t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">874
-</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">282
@@ -4390,35 +4425,36 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t xml:space="preserve">820
+</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">61
+</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4435,88 +4471,83 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4085
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">203
 </t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">23
 </t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">286
@@ -4543,13 +4574,13 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>855</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4566,13 +4597,13 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4590,13 +4621,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4614,31 +4644,31 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4649,54 +4679,52 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
-</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3328
-</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">643
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -4720,13 +4748,13 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
+          <t xml:space="preserve">3228
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -4744,19 +4772,19 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3713
+          <t xml:space="preserve">4373
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4768,7 +4796,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4780,31 +4808,37 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4815,13 +4849,13 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4839,19 +4873,19 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4862,19 +4896,19 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">2
+78
 </t>
         </is>
       </c>
@@ -4892,13 +4926,13 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">32720
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -4910,12 +4944,14 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4926,105 +4962,100 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>816</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">566
+</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">26
 </t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">566
-</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="Y33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">691
-</t>
-        </is>
-      </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5041,8 +5072,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3970
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -5058,7 +5088,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -5070,19 +5100,19 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -5100,82 +5130,84 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">477
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>455</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">832
+</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">54
+5
 </t>
         </is>
       </c>
@@ -5193,144 +5225,136 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3624
-</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>613</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">31
 </t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">786
-</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">2216
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">6
+</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5347,142 +5371,142 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">3989
 </t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2890
+</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">26
 </t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">854
-</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>885</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">3266
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -5497,138 +5521,140 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3989
+          <t xml:space="preserve">16835
 </t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t xml:space="preserve">561
+</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">059
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">924
+</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">1035
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">4325
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">627
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t xml:space="preserve">793
+</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
@@ -5646,139 +5672,141 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16835
+          <t xml:space="preserve">3367
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
+          <t xml:space="preserve">3600
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0029</t>
+          <t xml:space="preserve">2646
+</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1078
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13996
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>26201</t>
+          <t xml:space="preserve">252
+</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3437
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">657
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">2526
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>354</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3966
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -5796,91 +5824,85 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3367
-</t>
+          <t>427</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>415</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9251
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -5892,49 +5914,46 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5951,127 +5970,144 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">2024
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">2064
 </t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2221
+</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">2160
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
-        </is>
-      </c>
-      <c r="X40" s="2" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">813
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6088,142 +6124,143 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>0401</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">584
+</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">221
 </t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1001
-</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">26
 </t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="X41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">855
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6240,144 +6277,144 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4488
+          <t xml:space="preserve">442
+2 6
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>331</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>632</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6394,126 +6431,120 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">3413
+</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1781
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>663</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>611</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
@@ -6523,13 +6554,13 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6546,143 +6577,137 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="n"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9223
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">7335
 </t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t xml:space="preserve">815
+</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
@@ -6698,129 +6723,131 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1416
-</t>
-        </is>
-      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">777
+</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1656
+</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18256
+</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">372
+</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">215
 </t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="n"/>
-      <c r="Q45" s="2" t="n"/>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
+      <c r="S45" s="2" t="n"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">690
+</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2424
+</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="n"/>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1242
+</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">6 7
+57
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -6836,125 +6863,86 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">290
+</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2480
+</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0564</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">20 8
+</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">690
-</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="n"/>
+      <c r="Q46" s="2" t="n"/>
+      <c r="R46" s="2" t="n"/>
+      <c r="S46" s="2" t="n"/>
+      <c r="T46" s="2" t="n"/>
+      <c r="U46" s="2" t="n"/>
+      <c r="V46" s="2" t="n"/>
+      <c r="W46" s="2" t="n"/>
+      <c r="X46" s="2" t="n"/>
+      <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6972,78 +6960,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
-</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1111
-</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
           <t>Tot.</t>

--- a/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
@@ -626,36 +626,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">94375
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1312
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -667,7 +665,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -680,50 +678,49 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30226
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">637
-</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -734,8 +731,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -744,24 +740,9 @@
 </t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -774,51 +755,41 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">623
-</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
@@ -836,30 +807,26 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
-</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -871,46 +838,44 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="n"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t xml:space="preserve">741
+</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -928,13 +893,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4316
-</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
@@ -952,43 +916,38 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">606
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1203
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -1000,37 +959,36 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">12329
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">16089
 </t>
         </is>
       </c>
@@ -1042,30 +1000,31 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t xml:space="preserve">1850
+</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -1083,77 +1042,71 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">14373
 </t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">2330
 </t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1648
+</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">060
-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1502
-</t>
-        </is>
-      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1673
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">1876
 </t>
         </is>
       </c>
@@ -1165,7 +1118,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3189
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1177,13 +1130,13 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">20221
 </t>
         </is>
       </c>
@@ -1195,30 +1148,31 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">1276
+</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1779
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -1236,22 +1190,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">12972
+</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t xml:space="preserve">1262
+</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1262,13 +1220,14 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1279,66 +1238,66 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>245</t>
+          <t xml:space="preserve">1285
+</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18656
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">1205
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
+          <t xml:space="preserve">1877
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">1332
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1356,19 +1315,20 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1385,39 +1345,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">16665
 </t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">925
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8526
+</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t xml:space="preserve">805
+</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">155
@@ -1426,58 +1377,61 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">443
+</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t xml:space="preserve">1943
+</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
+          <t xml:space="preserve">1963
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4409
+          <t xml:space="preserve">14409
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1629
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
+          <t xml:space="preserve">11388
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t xml:space="preserve">16173
+</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">1329
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
+          <t xml:space="preserve">13609
 </t>
         </is>
       </c>
@@ -1489,31 +1443,16 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11261
+</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="n"/>
+      <c r="X9" s="2" t="n"/>
+      <c r="Y9" s="2" t="n"/>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1531,18 +1470,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t xml:space="preserve">3333
+</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">3051
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1553,12 +1493,14 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">1161
+</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1569,36 +1511,27 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5447
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1876
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
@@ -1610,40 +1543,42 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t xml:space="preserve">278
+</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">1264
+</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">2722
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">117
+</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1655,13 +1590,13 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8065
+          <t xml:space="preserve">1805
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -1679,30 +1614,31 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456
+          <t xml:space="preserve">14450
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">287
+</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1714,12 +1650,13 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -1729,12 +1666,7 @@
 </t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
+      <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">187
@@ -1743,26 +1675,25 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">1879
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>419</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1773,7 +1704,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">19819
 </t>
         </is>
       </c>
@@ -1785,19 +1716,19 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">1357
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
@@ -1809,16 +1740,11 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1975
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1845,18 +1771,20 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1867,7 +1795,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -1879,14 +1807,13 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1909,13 +1836,13 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2722
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
@@ -1933,41 +1860,37 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>85441</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t xml:space="preserve">53
+</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">1247
+</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">12844
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">977
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2304
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="n"/>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -1985,12 +1908,13 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t xml:space="preserve">393567
+</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
@@ -2014,31 +1938,31 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1176
+</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
@@ -2056,18 +1980,14 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1891
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -2079,7 +1999,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3247
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
@@ -2091,35 +2011,37 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">1614
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">1238
+</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1977
+</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2137,19 +2059,19 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
+          <t xml:space="preserve">139740
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">1325
 </t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2161,43 +2083,38 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -2209,7 +2126,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
@@ -2227,13 +2144,13 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2263,13 +2180,14 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t xml:space="preserve">1930
+</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2298,28 +2216,31 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t xml:space="preserve">295
+</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t xml:space="preserve">1208
+</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">1249
+</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -2331,19 +2252,18 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -2352,15 +2272,10 @@
           <t>9</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
+      <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -2384,13 +2299,13 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
+          <t xml:space="preserve">1638
 </t>
         </is>
       </c>
@@ -2402,30 +2317,31 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">12411
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t xml:space="preserve">1740
+</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -2443,19 +2359,19 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">119928
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">1499
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9291
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
@@ -2467,22 +2383,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
+          <t xml:space="preserve">1508
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1903
+</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -2491,13 +2402,13 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1609
+          <t xml:space="preserve">11009
 </t>
         </is>
       </c>
@@ -2509,48 +2420,49 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211222
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">4441
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">11428
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">1425
 </t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3687
+          <t xml:space="preserve">13687
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5334415</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2559,26 +2471,17 @@
 </t>
         </is>
       </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
+      <c r="W16" s="2" t="n"/>
+      <c r="X16" s="2" t="n"/>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
+          <t xml:space="preserve">14551
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -2596,9 +2499,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-3986
-</t>
+          <t>399</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2615,7 +2516,8 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">12249
+</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2625,42 +2527,44 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -2672,36 +2576,36 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2861
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">1737
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">1106
+</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2428
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
@@ -2713,19 +2617,19 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -2743,7 +2647,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">432
+          <t xml:space="preserve">4375
 </t>
         </is>
       </c>
@@ -2755,40 +2659,38 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1249
+</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">1871
+</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1395
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">40
+</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -2812,19 +2714,19 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2429
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -2836,30 +2738,31 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t xml:space="preserve">1631
+</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">2256
 </t>
         </is>
       </c>
@@ -2871,14 +2774,13 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-8 179
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2896,7 +2798,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4239
+          <t xml:space="preserve">14239
 </t>
         </is>
       </c>
@@ -2914,36 +2816,38 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">11248
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2954,25 +2858,24 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2996,8 +2899,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>621</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -3008,7 +2910,8 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t xml:space="preserve">1258
+</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -3019,21 +2922,19 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-44
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-818
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3051,42 +2952,43 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t xml:space="preserve">2568
+</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-1 8 4
-7
+          <t xml:space="preserve">1822
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3098,45 +3000,49 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t xml:space="preserve">124080
+</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">1890
+</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -3148,12 +3054,14 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t xml:space="preserve">707
+</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -3164,21 +3072,28 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t xml:space="preserve">1205
+</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="Z20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1672
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>13</t>
@@ -3193,13 +3108,14 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335
+          <t xml:space="preserve">14335
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">1308
+</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3214,16 +3130,21 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3233,12 +3154,7 @@
 </t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">188
@@ -3247,8 +3163,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3259,37 +3174,32 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1867
+</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">1301
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">417
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5310
+          <t xml:space="preserve">1510
 </t>
         </is>
       </c>
@@ -3301,30 +3211,30 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">1243
+</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">259
-8111
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t xml:space="preserve">1850
+</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3342,24 +3252,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">374 0
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>312</t>
+          <t xml:space="preserve">318
+</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3370,19 +3282,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -3394,7 +3306,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -3406,19 +3318,19 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8720
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -3436,13 +3348,14 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t xml:space="preserve">1564
+</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -3453,24 +3366,25 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">1855
 </t>
         </is>
       </c>
@@ -3494,28 +3408,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t xml:space="preserve">19255
+</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t xml:space="preserve">1531
+</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">928
+</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">11230
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t xml:space="preserve">1603
+</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -3532,101 +3450,83 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1355
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">499
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">1952
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8826
+          <t xml:space="preserve">18828
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4382
+          <t xml:space="preserve">14372
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1462
-</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29526
+          <t xml:space="preserve">12952
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="n"/>
+      <c r="W23" s="2" t="n"/>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">11267
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">14110
+</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -3644,7 +3544,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>58511</t>
+          <t xml:space="preserve">3851
+</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3661,18 +3562,19 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2246
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
@@ -3697,31 +3599,26 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8724
-</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1874
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -3739,19 +3636,19 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">1590
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
@@ -3763,19 +3660,19 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1822
+</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3790,65 +3687,143 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13740
+</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1257
+</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n"/>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="n"/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1204
+</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="n"/>
-      <c r="R25" s="2" t="n"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1313
+</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2431</t>
+        </is>
+      </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="n"/>
-      <c r="U25" s="2" t="n"/>
+          <t xml:space="preserve">1259
+</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9569
+</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="n"/>
-      <c r="X25" s="2" t="n"/>
-      <c r="Y25" s="2" t="n"/>
-      <c r="Z25" s="2" t="n"/>
+          <t xml:space="preserve">12242
+</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1209
+</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17476
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75
+</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3863,139 +3838,142 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">3298
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3261
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">247
+</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1720
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2604
+          <t xml:space="preserve">19492
 </t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t xml:space="preserve">244
+</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t xml:space="preserve">1800
+</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">1246
+</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -4013,145 +3991,140 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t xml:space="preserve">8
+</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">7208
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">1875
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">2060
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">1808
 </t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4168,140 +4141,145 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t xml:space="preserve">93893
+</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1398
+</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1213
+</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1874
+</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
 </t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">825
-</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1649
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>081</t>
+          <t xml:space="preserve">820
+</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -4319,59 +4297,61 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3893
+          <t xml:space="preserve">4085
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12396
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -4383,25 +4363,25 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1213
+</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -4413,47 +4393,49 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">12265
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">1626
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>260</t>
+          <t xml:space="preserve">1255
+</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -4471,139 +4453,145 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t xml:space="preserve">18564
+</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t xml:space="preserve">1503
+</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">978
+</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">1525
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">1919
+</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1800
+</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">11032
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">14419
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">11385
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">11137
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">13328
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1645
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t xml:space="preserve">18231
+</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">11243
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">13998
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
@@ -4621,140 +4609,136 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>064</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1884
+</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t xml:space="preserve">1666
+</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -4778,137 +4762,127 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+          <t>8651</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">1566
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">1264
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t xml:space="preserve">691
+</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-78
+          <t xml:space="preserve">11188
 </t>
         </is>
       </c>
@@ -4926,136 +4900,137 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32720
+          <t xml:space="preserve">13970
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">337
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>495</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">267
+</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>284</t>
+          <t xml:space="preserve">874
+</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1329
+</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
+          <t xml:space="preserve">19477
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t xml:space="preserve">1261
+</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">258
 </t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5072,86 +5047,82 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t xml:space="preserve">3624
+</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">304
+</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1873
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">261
@@ -5160,13 +5131,13 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
@@ -5178,36 +5149,36 @@
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>0554</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t xml:space="preserve">233
+</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">1832
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-5
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -5225,30 +5196,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t xml:space="preserve">1879
+</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -5257,22 +5230,28 @@
 </t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t xml:space="preserve">2010
+</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -5283,24 +5262,24 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">2093
+</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -5312,7 +5291,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
@@ -5330,7 +5309,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -5342,18 +5321,19 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1885
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -5377,24 +5357,25 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t xml:space="preserve">1200
+</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5418,7 +5399,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5436,13 +5417,13 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
@@ -5454,19 +5435,19 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">25938
 </t>
         </is>
       </c>
@@ -5484,26 +5465,31 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2050
+</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1221
+</t>
+        </is>
+      </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3266
+          <t xml:space="preserve">1782
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5521,28 +5507,13 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16835
-</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">561
-</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">059
-</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">355
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">116835
+</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">492
@@ -5551,7 +5522,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">1924
 </t>
         </is>
       </c>
@@ -5569,7 +5540,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1608
 </t>
         </is>
       </c>
@@ -5579,53 +5550,47 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">965
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1172
-</t>
-        </is>
-      </c>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4325
+          <t xml:space="preserve">14325
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t xml:space="preserve">1396
+</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">1154
+</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">627
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>34311</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t xml:space="preserve">1657
+</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -5634,27 +5599,17 @@
 </t>
         </is>
       </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">721
-</t>
-        </is>
-      </c>
+      <c r="W37" s="2" t="n"/>
+      <c r="X37" s="2" t="n"/>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
+          <t xml:space="preserve">3966
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">3424
 </t>
         </is>
       </c>
@@ -5678,20 +5633,19 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3600
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2646
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5702,28 +5656,22 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12111
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -5732,30 +5680,31 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">1875
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
@@ -5767,46 +5716,49 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1252
+</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1687
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">252
 </t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">687
-</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2526
-</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">793
+</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -5824,7 +5776,8 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t xml:space="preserve">14008
+</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5835,74 +5788,79 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">525
+</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1205
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">195
 </t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">910
+</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">1304
 </t>
         </is>
       </c>
@@ -5914,13 +5872,13 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -5931,29 +5889,32 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t xml:space="preserve">1268
+</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t xml:space="preserve">784
+</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5970,19 +5931,19 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">744
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
@@ -5994,31 +5955,30 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -6036,25 +5996,25 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -6072,7 +6032,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">1897
 </t>
         </is>
       </c>
@@ -6090,24 +6050,26 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6124,7 +6086,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">14488
 </t>
         </is>
       </c>
@@ -6136,31 +6098,32 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">130
+</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -6171,12 +6134,13 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0401</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -6188,7 +6152,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -6212,7 +6176,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -6224,8 +6188,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
-</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -6236,30 +6199,30 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1740
+</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6277,144 +6240,143 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-2 6
-</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">328
+</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">19249
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>028</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">2890
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">1300
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t xml:space="preserve">275
+</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6431,23 +6393,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
+          <t xml:space="preserve">23413
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t xml:space="preserve">1320
+</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">1886
+</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -6458,108 +6423,115 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1247
+</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1230
+</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27914
+</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="X43" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1828
+</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">946
 </t>
         </is>
       </c>
@@ -6583,19 +6555,19 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t xml:space="preserve">1239
+</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -6612,7 +6584,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -6624,93 +6596,82 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="n"/>
+          <t>3901</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">2286
 </t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7335
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">738
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="n"/>
+      <c r="Y44" s="2" t="n"/>
+      <c r="Z44" s="2" t="n"/>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6723,45 +6684,26 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168711
+</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
@@ -6773,81 +6715,71 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18256
-</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
+          <t xml:space="preserve">102342
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">11674
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">16912
+</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1297
+</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">262
 </t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="n"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">40844
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2424
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="n"/>
       <c r="W45" s="2" t="n"/>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">1848324382
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 7
-57
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -6865,12 +6797,13 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">3117
+</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -6882,14 +6815,19 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2480
-</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="n"/>
+          <t xml:space="preserve">1240
+</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
@@ -6901,26 +6839,26 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">194
 </t>
         </is>
       </c>
-      <c r="M46" s="2" t="n"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 8
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -6930,22 +6868,62 @@
 </t>
         </is>
       </c>
-      <c r="P46" s="2" t="n"/>
-      <c r="Q46" s="2" t="n"/>
-      <c r="R46" s="2" t="n"/>
-      <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="n"/>
-      <c r="V46" s="2" t="n"/>
-      <c r="W46" s="2" t="n"/>
-      <c r="X46" s="2" t="n"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2062
+</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2216
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1690
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2242
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="Y46" s="2" t="n"/>
-      <c r="Z46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -6958,19 +6936,6 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
           <t>Tot.</t>

--- a/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
@@ -626,34 +626,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94375
+          <t xml:space="preserve">837
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1312
+          <t xml:space="preserve">3182
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1242
+</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t xml:space="preserve">140
+</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">9124 11
 </t>
         </is>
       </c>
@@ -665,11 +668,16 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n"/>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 8
+</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">176
@@ -678,25 +686,25 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
+          <t xml:space="preserve">11785
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -708,19 +716,20 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t xml:space="preserve">637
+</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -731,7 +740,8 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t xml:space="preserve">277
+</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -755,10 +765,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -770,7 +784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">2135
 </t>
         </is>
       </c>
@@ -782,20 +796,15 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1874
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -813,17 +822,22 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900
-</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n"/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">205
@@ -838,19 +852,19 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -860,16 +874,21 @@
 </t>
         </is>
       </c>
-      <c r="W5" s="2" t="n"/>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">2725
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
+          <t xml:space="preserve">7261
 </t>
         </is>
       </c>
@@ -893,12 +912,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t xml:space="preserve">8316
+</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -922,32 +942,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">026
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1203
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -959,54 +984,55 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12329
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t xml:space="preserve">259
+</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16089
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -1018,13 +1044,13 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -1042,54 +1068,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14373
+          <t xml:space="preserve">1437
 </t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2330
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t xml:space="preserve">250
+</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648
-</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n"/>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 82
+</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">1123
+</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1100,13 +1134,13 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1673
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
@@ -1118,7 +1152,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1130,13 +1164,13 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20221
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
@@ -1148,25 +1182,20 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
-</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1241
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1779
+          <t xml:space="preserve">17729
 </t>
         </is>
       </c>
@@ -1190,7 +1219,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12972
+          <t xml:space="preserve">989716
 </t>
         </is>
       </c>
@@ -1202,13 +1231,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -1226,7 +1255,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1238,13 +1267,13 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1256,43 +1285,44 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1877
+          <t xml:space="preserve">877
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1332
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25241</t>
+          <t xml:space="preserve">954
+</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1315,7 +1345,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -1325,12 +1355,7 @@
 </t>
         </is>
       </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+      <c r="Z8" s="2" t="n"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1345,21 +1370,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16665
+          <t xml:space="preserve">1666
 </t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8526
-</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
+          <t xml:space="preserve">11526
+</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1368,7 +1404,12 @@
 </t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2112
+</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">155
@@ -1377,61 +1418,61 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">443
+          <t xml:space="preserve">440
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1963
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14409
+          <t xml:space="preserve">18409
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1629
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11388
+          <t xml:space="preserve">1388
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16173
+          <t xml:space="preserve">12173
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">18319
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13609
+          <t xml:space="preserve">3609
 </t>
         </is>
       </c>
@@ -1443,16 +1484,26 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11261
-</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="n"/>
+          <t xml:space="preserve">1261
+</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="n"/>
-      <c r="Y9" s="2" t="n"/>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114184
+</t>
+        </is>
+      </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
@@ -1470,19 +1521,20 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3051
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1499,13 +1551,13 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -1515,10 +1567,15 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="2" t="n"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -1528,10 +1585,15 @@
 </t>
         </is>
       </c>
-      <c r="N10" s="2" t="n"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -1549,19 +1611,19 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2722
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
@@ -1573,7 +1635,8 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">252
+</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1584,13 +1647,13 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">8259
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805
+          <t xml:space="preserve">805
 </t>
         </is>
       </c>
@@ -1614,7 +1677,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14450
+          <t xml:space="preserve">14451
 </t>
         </is>
       </c>
@@ -1632,7 +1695,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -1650,23 +1713,28 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">187
@@ -1675,76 +1743,81 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">2467
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t xml:space="preserve">279
+</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">23 08
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19819
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1975
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="n"/>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1759,13 +1832,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3836
-</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">1981
 </t>
         </is>
       </c>
@@ -1777,25 +1849,25 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -1807,13 +1879,14 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1836,13 +1909,13 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -1860,7 +1933,8 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85441</t>
+          <t xml:space="preserve">854
+</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1871,29 +1945,29 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12844
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304
-</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="n"/>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1977
+</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="n"/>
       <c r="AA12" t="inlineStr">
         <is>
           <t>7</t>
@@ -1908,13 +1982,13 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">393567
+          <t xml:space="preserve">0856
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -1938,7 +2012,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -1950,19 +2024,19 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">053
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1980,14 +2054,14 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
+          <t xml:space="preserve">891
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="n"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2011,19 +2085,19 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2035,13 +2109,13 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2059,13 +2133,13 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139740
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1325
+          <t xml:space="preserve">2325
 </t>
         </is>
       </c>
@@ -2089,17 +2163,22 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">57
@@ -2108,13 +2187,13 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -2126,14 +2205,13 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2150,7 +2228,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -2210,7 +2288,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335
+          <t xml:space="preserve">16433
 </t>
         </is>
       </c>
@@ -2222,13 +2300,13 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">2028
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2240,24 +2318,25 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">34
+</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
@@ -2269,13 +2348,19 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2299,13 +2384,13 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1638
+          <t xml:space="preserve">638
 </t>
         </is>
       </c>
@@ -2317,13 +2402,13 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12411
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2335,7 +2420,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">17410
 </t>
         </is>
       </c>
@@ -2359,37 +2444,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119928
+          <t xml:space="preserve">1992
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
+          <t xml:space="preserve">11299
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">9918
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1508
+          <t xml:space="preserve">508
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2408,43 +2493,42 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11009
-</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">1946
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
+          <t xml:space="preserve">10559
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4441
+          <t xml:space="preserve">44641
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">11230
 </t>
         </is>
       </c>
@@ -2456,13 +2540,14 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13687
+          <t xml:space="preserve">3687
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5334415</t>
+          <t xml:space="preserve">531
+</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2471,11 +2556,21 @@
 </t>
         </is>
       </c>
-      <c r="W16" s="2" t="n"/>
-      <c r="X16" s="2" t="n"/>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1151
+</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1375
+</t>
+        </is>
+      </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14551
+          <t xml:space="preserve">4551
 </t>
         </is>
       </c>
@@ -2499,12 +2594,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
@@ -2516,15 +2611,11 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12249
-</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">181
@@ -2533,7 +2624,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2543,28 +2634,23 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1202
-</t>
-        </is>
-      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2576,13 +2662,14 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t xml:space="preserve">1820
+</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2593,7 +2680,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -2605,7 +2692,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">2482
 </t>
         </is>
       </c>
@@ -2647,44 +2734,43 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
-</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1871
-</t>
-        </is>
-      </c>
+          <t>8441</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1713
+</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1395
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -2696,37 +2782,36 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2738,13 +2823,13 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -2762,13 +2847,13 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">4113
 </t>
         </is>
       </c>
@@ -2798,13 +2883,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14239
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">9225
 </t>
         </is>
       </c>
@@ -2816,19 +2900,19 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11248
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -2840,13 +2924,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
@@ -2858,7 +2941,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -2870,36 +2953,38 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">875
+</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">2618
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">12953
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t xml:space="preserve">540
+</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2910,7 +2995,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">16558
 </t>
         </is>
       </c>
@@ -2922,22 +3007,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>12</t>
@@ -2952,13 +3032,13 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568
+          <t xml:space="preserve">8568
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
@@ -2970,7 +3050,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -2982,7 +3062,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2994,31 +3074,26 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124080
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3036,19 +3111,19 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3060,7 +3135,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">95 1
 </t>
         </is>
       </c>
@@ -3072,7 +3147,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -3084,7 +3159,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672
+          <t xml:space="preserve">672
 </t>
         </is>
       </c>
@@ -3108,13 +3183,13 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14335
+          <t xml:space="preserve">433
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -3138,13 +3213,13 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3154,7 +3229,12 @@
 </t>
         </is>
       </c>
-      <c r="K21" s="2" t="n"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">188
@@ -3163,7 +3243,8 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3174,14 +3255,19 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1867
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n"/>
+          <t xml:space="preserve">867
+</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
@@ -3199,7 +3285,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -3211,13 +3297,14 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
@@ -3252,8 +3339,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374 0
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3262,12 +3348,7 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">245
@@ -3276,25 +3357,25 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3324,73 +3405,73 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">302
+</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">564
+</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1935
+</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1216
 </t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302
-</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1242
-</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1564
-</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1216
-</t>
-        </is>
-      </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -3420,19 +3501,19 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
+          <t xml:space="preserve">160274
 </t>
         </is>
       </c>
@@ -3450,48 +3531,58 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1355
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1952
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18828
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14372
+          <t xml:space="preserve">11372
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="n"/>
-      <c r="R23" s="2" t="n"/>
+          <t xml:space="preserve">15357
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1462
+</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11451
+</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -3500,7 +3591,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12952
+          <t xml:space="preserve">2952
 </t>
         </is>
       </c>
@@ -3510,17 +3601,27 @@
 </t>
         </is>
       </c>
-      <c r="V23" s="2" t="n"/>
-      <c r="W23" s="2" t="n"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2107
+</t>
+        </is>
+      </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11267
+          <t xml:space="preserve">2267
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14110
+          <t xml:space="preserve">18110
 </t>
         </is>
       </c>
@@ -3544,13 +3645,13 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3851
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -3562,19 +3663,19 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2246
+          <t xml:space="preserve">846
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -3586,11 +3687,16 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n"/>
+          <t xml:space="preserve">51
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -3599,26 +3705,31 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
-</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="n"/>
+          <t xml:space="preserve">874
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -3636,19 +3747,19 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1590
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3660,19 +3771,15 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
-</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1822
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">54
+</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3689,36 +3796,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13740
+          <t xml:space="preserve">3740
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">421
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3730,11 +3838,16 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n"/>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81414 6
+</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">195
@@ -3749,7 +3862,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -3761,30 +3874,31 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1313
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t xml:space="preserve">1040
+</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9569
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
@@ -3796,13 +3910,13 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3814,13 +3928,13 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17476
+          <t xml:space="preserve">1748
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">756
 </t>
         </is>
       </c>
@@ -3838,7 +3952,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
+          <t xml:space="preserve">3292
 </t>
         </is>
       </c>
@@ -3850,8 +3964,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3868,13 +3981,13 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1720
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3886,7 +3999,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -3898,24 +4011,25 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19492
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3939,38 +4053,35 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">68
+</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1811
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">176
@@ -3991,7 +4102,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">9522
 </t>
         </is>
       </c>
@@ -4003,13 +4114,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1924
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4025,10 +4136,15 @@
 </t>
         </is>
       </c>
-      <c r="I27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4040,7 +4156,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -4052,31 +4168,31 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4088,31 +4204,30 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1006
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">2098
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -4124,7 +4239,8 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">54
+</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4141,7 +4257,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93893
+          <t xml:space="preserve">2889
 </t>
         </is>
       </c>
@@ -4153,8 +4269,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -4171,25 +4286,25 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -4207,19 +4322,19 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">82813
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -4231,7 +4346,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -4243,26 +4358,25 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649
+          <t xml:space="preserve">649
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>556</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
@@ -4273,7 +4387,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -4297,7 +4411,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4085
+          <t xml:space="preserve">1408
 </t>
         </is>
       </c>
@@ -4309,52 +4423,51 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8229
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">203
 </t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1249
-</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192
@@ -4363,7 +4476,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -4375,13 +4488,13 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -4393,7 +4506,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12265
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -4411,7 +4524,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -4423,13 +4536,13 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">81828
 </t>
         </is>
       </c>
@@ -4453,37 +4566,37 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18564
+          <t xml:space="preserve">118364
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1503
+          <t xml:space="preserve">1505
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">12241
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1525
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4501,13 +4614,13 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4519,55 +4632,55 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11032
+          <t xml:space="preserve">91034
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14419
+          <t xml:space="preserve">142419
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11137
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13328
+          <t xml:space="preserve">3328
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18231
+          <t xml:space="preserve">11231
 </t>
         </is>
       </c>
@@ -4579,14 +4692,12 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11243
-</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13998
-</t>
+          <t>394</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4609,12 +4720,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -4626,18 +4737,20 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t xml:space="preserve">105
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t xml:space="preserve">11824
+</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4652,10 +4765,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="n"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -4667,13 +4785,13 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>064</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4684,7 +4802,7 @@
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4696,52 +4814,46 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
+          <t xml:space="preserve">666
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="n"/>
       <c r="AA31" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4756,49 +4868,55 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">9437
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n"/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4810,23 +4928,28 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">4215
 </t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="n"/>
+          <t xml:space="preserve">884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">310
@@ -4835,7 +4958,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -4847,24 +4970,25 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">5606
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">2682
+</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">11288
 </t>
         </is>
       </c>
@@ -4876,13 +5000,13 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">1691
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11188
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -4900,48 +5024,54 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13970
+          <t xml:space="preserve">3971
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">2657
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n"/>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1011
 </t>
         </is>
       </c>
@@ -4953,12 +5083,13 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -4976,42 +5107,43 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">239
 </t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19477
+          <t xml:space="preserve">477
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -5023,7 +5155,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -5047,13 +5179,13 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3624
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -5071,19 +5203,19 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -5095,7 +5227,8 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">1024
+</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -5118,11 +5251,16 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1873
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="n"/>
+          <t xml:space="preserve">873
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">261
@@ -5131,31 +5269,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">78868
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0554</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -5166,19 +5305,19 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">2272
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
+          <t xml:space="preserve">18328
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -5202,55 +5341,55 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -5262,24 +5401,25 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2093
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t xml:space="preserve">834
+</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -5291,7 +5431,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -5303,25 +5443,25 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -5333,7 +5473,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -5357,19 +5497,18 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">9243
 </t>
         </is>
       </c>
@@ -5393,13 +5532,13 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5417,13 +5556,13 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -5435,25 +5574,25 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25938
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
+          <t xml:space="preserve">8225
 </t>
         </is>
       </c>
@@ -5465,7 +5604,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050
+          <t xml:space="preserve">2958
 </t>
         </is>
       </c>
@@ -5477,22 +5616,17 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">8468
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1782
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">782
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="n"/>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -5511,9 +5645,24 @@
 </t>
         </is>
       </c>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14501
+</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1202
+</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1255
+</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">492
@@ -5522,7 +5671,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924
+          <t xml:space="preserve">92241
 </t>
         </is>
       </c>
@@ -5540,7 +5689,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1608
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5550,11 +5699,21 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13965
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14325
+          <t xml:space="preserve">4375
 </t>
         </is>
       </c>
@@ -5566,7 +5725,7 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1396
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -5578,18 +5737,19 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>34311</t>
+          <t xml:space="preserve">3437
+</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657
+          <t xml:space="preserve">657
 </t>
         </is>
       </c>
@@ -5599,8 +5759,18 @@
 </t>
         </is>
       </c>
-      <c r="W37" s="2" t="n"/>
-      <c r="X37" s="2" t="n"/>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1271
+</t>
+        </is>
+      </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3966
@@ -5609,7 +5779,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3424
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -5645,7 +5815,8 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5656,22 +5827,28 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12111
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n"/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -5680,25 +5857,25 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19 3
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -5716,19 +5893,19 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1687
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
@@ -5740,7 +5917,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">2 24 2
 </t>
         </is>
       </c>
@@ -5752,13 +5929,13 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
+          <t xml:space="preserve">1793
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5776,19 +5953,19 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
+          <t xml:space="preserve">140018
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">4118
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -5800,7 +5977,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -5810,27 +5987,22 @@
 </t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">525
-</t>
-        </is>
-      </c>
+      <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -5842,7 +6014,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5854,19 +6026,19 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -5878,7 +6050,8 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t xml:space="preserve">5345
+</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -5889,31 +6062,31 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">976
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">1754
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -5937,13 +6110,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>94446</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -5955,30 +6127,31 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">539
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -5996,7 +6169,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -6008,13 +6181,13 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -6032,7 +6205,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
@@ -6044,34 +6217,29 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1906
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">12172
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
-        </is>
-      </c>
-      <c r="Z40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1815
+</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="n"/>
       <c r="AA40" t="inlineStr">
         <is>
           <t>27</t>
@@ -6086,14 +6254,13 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14488
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6116,31 +6283,31 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -6176,7 +6343,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -6188,7 +6355,8 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t xml:space="preserve">584
+</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -6199,7 +6367,8 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -6210,7 +6379,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -6240,12 +6409,13 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -6257,13 +6427,13 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -6275,30 +6445,31 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>028</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -6310,7 +6481,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -6334,19 +6505,19 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">2282
 </t>
         </is>
       </c>
@@ -6358,27 +6529,23 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1104
+</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">187080
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="n"/>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -6393,19 +6560,19 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23413
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -6423,19 +6590,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6471,19 +6638,19 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -6495,32 +6662,26 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
-</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27914
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -6531,7 +6692,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -6549,25 +6710,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -6584,7 +6746,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">0808
 </t>
         </is>
       </c>
@@ -6608,17 +6770,20 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">2008
+</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t xml:space="preserve">1890
+</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -6629,13 +6794,13 @@
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2286
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6647,19 +6812,19 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">18223
 </t>
         </is>
       </c>
@@ -6686,88 +6851,123 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168711
-</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
+          <t xml:space="preserve">188411
+</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8411
+</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1740
+</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1602
+</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1056
+</t>
+        </is>
+      </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">28161
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">121804
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="n"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101092106191
+</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102342
+          <t xml:space="preserve">02041
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11674
+          <t xml:space="preserve">168084
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16912
+          <t xml:space="preserve">12572
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">12917
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">183179
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40844
+          <t xml:space="preserve">448414
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="n"/>
-      <c r="W45" s="2" t="n"/>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11222
+</t>
+        </is>
+      </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848324382
+          <t xml:space="preserve">9247
 </t>
         </is>
       </c>
@@ -6797,13 +6997,13 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
+          <t xml:space="preserve">5117
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -6815,35 +7015,40 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11226
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -6858,8 +7063,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -6876,13 +7080,13 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2062
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -6894,7 +7098,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
@@ -6906,22 +7110,17 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2188
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="n"/>
       <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3182
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -644,7 +644,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -656,7 +656,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9124 11
+          <t xml:space="preserve">91124 1
 </t>
         </is>
       </c>
@@ -674,13 +674,13 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 8
+          <t xml:space="preserve">8 8 8
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1756
 </t>
         </is>
       </c>
@@ -692,7 +692,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11785
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -740,7 +740,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -784,7 +784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -796,18 +796,13 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">191
@@ -822,7 +817,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -832,12 +827,7 @@
 </t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
+      <c r="P5" s="2" t="n"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">205
@@ -864,7 +854,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -876,19 +866,19 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2725
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7261
+          <t xml:space="preserve">741
 </t>
         </is>
       </c>
@@ -912,7 +902,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8316
+          <t xml:space="preserve">4326
 </t>
         </is>
       </c>
@@ -942,25 +932,25 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">026
+          <t xml:space="preserve">096
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -1014,13 +1004,13 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">619
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1068,19 +1058,19 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437
+          <t xml:space="preserve">437
 </t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1092,19 +1082,19 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">1848
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1122,25 +1112,25 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">2620
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">876
 </t>
         </is>
       </c>
@@ -1195,7 +1185,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17729
+          <t xml:space="preserve">7279
 </t>
         </is>
       </c>
@@ -1219,7 +1209,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989716
+          <t xml:space="preserve">297 6
 </t>
         </is>
       </c>
@@ -1231,28 +1221,28 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">172
 </t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -1279,7 +1269,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1376,13 +1366,13 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11526
+          <t xml:space="preserve">1526
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1406,7 +1396,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -1442,7 +1432,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18409
+          <t xml:space="preserve">4409
 </t>
         </is>
       </c>
@@ -1460,13 +1450,13 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12173
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18319
+          <t xml:space="preserve">12319
 </t>
         </is>
       </c>
@@ -1494,16 +1484,21 @@
 </t>
         </is>
       </c>
-      <c r="X9" s="2" t="n"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114184
+          <t xml:space="preserve">1141024
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">388
 </t>
         </is>
       </c>
@@ -1551,28 +1546,18 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -1587,13 +1572,13 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">2193
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
@@ -1647,7 +1632,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -1659,7 +1644,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -1677,7 +1662,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14451
+          <t xml:space="preserve">24451
 </t>
         </is>
       </c>
@@ -1707,7 +1692,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1852
 </t>
         </is>
       </c>
@@ -1719,13 +1704,13 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -1743,7 +1728,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2467
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -1755,7 +1740,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1767,7 +1752,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 08
+          <t xml:space="preserve">25 8
 </t>
         </is>
       </c>
@@ -1779,13 +1764,13 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">587
 </t>
         </is>
       </c>
@@ -1797,7 +1782,8 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">247 16
+</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -1814,7 +1800,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -1832,12 +1818,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -1861,7 +1847,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1879,7 +1865,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -1963,7 +1949,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">977
 </t>
         </is>
       </c>
@@ -1982,7 +1968,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0856
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -2000,7 +1986,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">2355
 </t>
         </is>
       </c>
@@ -2024,13 +2010,13 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">053
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2103,13 +2089,13 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -2139,7 +2125,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2325
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -2163,7 +2149,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2173,12 +2159,7 @@
 </t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+      <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">57
@@ -2193,7 +2174,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -2211,7 +2192,8 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2228,7 +2210,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2258,13 +2240,13 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -2288,7 +2270,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16433
+          <t xml:space="preserve">433
 </t>
         </is>
       </c>
@@ -2300,7 +2282,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -2312,19 +2294,19 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2336,7 +2318,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 8
+          <t xml:space="preserve">16 8
 </t>
         </is>
       </c>
@@ -2396,7 +2378,7 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
@@ -2420,7 +2402,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17410
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -2450,19 +2432,19 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11299
+          <t xml:space="preserve">192499
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9918
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
@@ -2478,7 +2460,12 @@
 </t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -2493,30 +2480,30 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>112</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
+          <t xml:space="preserve">9246
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10559
+          <t xml:space="preserve">1058
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44641
+          <t xml:space="preserve">4448
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -2528,7 +2515,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2594,12 +2581,13 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">398
+</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2615,7 +2603,12 @@
 </t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">181
@@ -2624,18 +2617,21 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -2650,7 +2646,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2668,7 +2664,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">282240
 </t>
         </is>
       </c>
@@ -2680,25 +2676,25 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2482
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -2710,13 +2706,13 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -2734,7 +2730,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2746,43 +2742,47 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>149</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1713
-</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2799,13 +2799,13 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2841,19 +2841,19 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">2506
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4113
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9225
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -2924,7 +2924,8 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2965,19 +2966,19 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2618
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12953
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -2995,7 +2996,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16558
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -3013,7 +3014,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -3032,13 +3033,13 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8568
+          <t xml:space="preserve">9568
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -3050,7 +3051,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3062,7 +3063,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3072,13 +3073,12 @@
 </t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -3099,19 +3099,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">2890
 </t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3123,13 +3123,13 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
+          <t xml:space="preserve">7072
 </t>
         </is>
       </c>
@@ -3147,8 +3147,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -3231,7 +3230,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3291,7 +3290,7 @@
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2089
 </t>
         </is>
       </c>
@@ -3315,7 +3314,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">8508
 </t>
         </is>
       </c>
@@ -3339,7 +3338,8 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>344</t>
+          <t xml:space="preserve">3741
+</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3348,7 +3348,11 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">245
@@ -3357,7 +3361,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1846
 </t>
         </is>
       </c>
@@ -3369,7 +3373,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3447,19 +3451,19 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1935
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -3471,7 +3475,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -3495,13 +3499,13 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">1551
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160274
+          <t xml:space="preserve">6059
 </t>
         </is>
       </c>
@@ -3537,7 +3541,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">4953
 </t>
         </is>
       </c>
@@ -3561,25 +3565,25 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11372
+          <t xml:space="preserve">4372
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15357
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11451
+          <t xml:space="preserve">11431
 </t>
         </is>
       </c>
@@ -3603,13 +3607,13 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2107
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -3621,7 +3625,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18110
+          <t xml:space="preserve">14110
 </t>
         </is>
       </c>
@@ -3645,25 +3649,25 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -3675,7 +3679,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -3687,7 +3691,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -3711,7 +3715,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -3723,13 +3727,13 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3741,7 +3745,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23 8
 </t>
         </is>
       </c>
@@ -3802,19 +3806,19 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -3826,40 +3830,40 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 6
+</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81414 6
-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">204
@@ -3868,25 +3872,25 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">31 5
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -3898,19 +3902,19 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3922,7 +3926,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -3934,7 +3938,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
@@ -4017,7 +4021,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">89 2
 </t>
         </is>
       </c>
@@ -4047,7 +4051,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -4059,7 +4063,7 @@
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -4102,25 +4106,24 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9522
+          <t xml:space="preserve">3548
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4132,13 +4135,13 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -4174,7 +4177,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
@@ -4192,7 +4195,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -4210,18 +4213,18 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1006
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>634</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -4233,7 +4236,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -4257,7 +4260,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -4269,7 +4272,8 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -4280,19 +4284,19 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4322,7 +4326,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82813
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -4334,7 +4338,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4364,7 +4368,7 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -4376,18 +4380,18 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -4411,30 +4415,29 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8229
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4476,7 +4479,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4488,7 +4491,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4506,13 +4509,13 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">2245
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1626
+          <t xml:space="preserve">624
 </t>
         </is>
       </c>
@@ -4536,19 +4539,19 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81828
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
@@ -4566,7 +4569,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118364
+          <t xml:space="preserve">118564
 </t>
         </is>
       </c>
@@ -4578,13 +4581,13 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
@@ -4602,7 +4605,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4620,7 +4623,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">9296
 </t>
         </is>
       </c>
@@ -4632,25 +4635,25 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91034
+          <t xml:space="preserve">1034
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142419
+          <t xml:space="preserve">4419
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">2385
 </t>
         </is>
       </c>
@@ -4674,13 +4677,13 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
@@ -4692,12 +4695,12 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>613</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>439</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4720,19 +4723,18 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>334</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>096</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4749,7 +4751,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11824
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -4765,15 +4767,10 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -4791,12 +4788,13 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t xml:space="preserve">884
+</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4814,7 +4812,8 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4825,13 +4824,13 @@
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">28246
 </t>
         </is>
       </c>
@@ -4843,13 +4842,13 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
@@ -4868,13 +4867,13 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9437
+          <t xml:space="preserve">1437
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">4128
 </t>
         </is>
       </c>
@@ -4886,7 +4885,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -4904,7 +4903,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -4916,85 +4915,85 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1285
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">566
+</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">19
 </t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4215
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5606
-</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2682
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11288
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -5006,7 +5005,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -5024,13 +5023,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3971
-</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
@@ -5042,7 +5040,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -5054,14 +5052,13 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -5071,7 +5068,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1011
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5113,7 +5110,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">2389
 </t>
         </is>
       </c>
@@ -5155,13 +5152,13 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">17276
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -5185,7 +5182,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -5203,7 +5200,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5227,7 +5224,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5269,7 +5266,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5281,19 +5278,19 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78868
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
@@ -5305,13 +5302,13 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2272
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18328
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -5335,7 +5332,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
@@ -5401,13 +5398,13 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
@@ -5443,19 +5440,19 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -5467,13 +5464,13 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5503,24 +5500,24 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">19 0 1
 </t>
         </is>
       </c>
@@ -5538,7 +5535,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
@@ -5556,7 +5553,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -5592,7 +5589,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
@@ -5604,19 +5601,19 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2958
+          <t xml:space="preserve">2580
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8468
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -5647,19 +5644,19 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14501
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">002
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -5671,7 +5668,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92241
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -5701,13 +5698,13 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -5725,7 +5722,7 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">1396
 </t>
         </is>
       </c>
@@ -5737,7 +5734,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">12560
 </t>
         </is>
       </c>
@@ -5827,7 +5824,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5839,13 +5836,12 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -5893,7 +5889,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -5905,7 +5901,7 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -5917,7 +5913,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 24 2
+          <t xml:space="preserve">224 1
 </t>
         </is>
       </c>
@@ -5929,7 +5925,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1793
+          <t xml:space="preserve">793
 </t>
         </is>
       </c>
@@ -5953,13 +5949,13 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140018
+          <t xml:space="preserve">4008
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4118
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -5977,20 +5973,20 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">1585
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1821
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -6002,7 +5998,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6014,7 +6010,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">2884
 </t>
         </is>
       </c>
@@ -6026,31 +6022,31 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5345
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
@@ -6074,19 +6070,19 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">976
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1754
+          <t xml:space="preserve">784
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -6110,7 +6106,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>94446</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6127,109 +6123,109 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1890
+</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">897
+</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2083
+</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1906
-</t>
-        </is>
-      </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12172
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -6254,13 +6250,13 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">648
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>943</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6271,7 +6267,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -6283,25 +6279,25 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6379,13 +6375,13 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -6409,13 +6405,13 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">14645
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -6451,7 +6447,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -6505,22 +6501,22 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2282
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500
+</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">222
 </t>
         </is>
       </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">500
-</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2282
-</t>
-        </is>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">275
@@ -6535,13 +6531,13 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187080
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -6560,7 +6556,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
+          <t xml:space="preserve">341
 </t>
         </is>
       </c>
@@ -6602,7 +6598,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -6638,7 +6634,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -6666,7 +6662,12 @@
 </t>
         </is>
       </c>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">230
@@ -6681,7 +6682,7 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>531</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -6710,7 +6711,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
@@ -6746,13 +6747,13 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0808
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -6770,26 +6771,24 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1098
 </t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
-</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -6800,7 +6799,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6812,28 +6811,23 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18223
-</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr"/>
       <c r="X44" s="2" t="n"/>
       <c r="Y44" s="2" t="n"/>
       <c r="Z44" s="2" t="n"/>
@@ -6851,43 +6845,42 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188411
+          <t xml:space="preserve">1682111
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8411
+          <t xml:space="preserve">8251
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1833
 </t>
         </is>
       </c>
@@ -6899,87 +6892,92 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28161
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121804
+          <t xml:space="preserve">19104
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="n"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101092106191
+          <t xml:space="preserve">100921059
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02041
+          <t xml:space="preserve">0342
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168084
+          <t xml:space="preserve">1404
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12572
+          <t xml:space="preserve">2575
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12917
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183179
+          <t xml:space="preserve">13820
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">448414
+          <t xml:space="preserve">4840
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1822
+</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">815
 </t>
         </is>
       </c>
-      <c r="V45" s="2" t="n"/>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11222
-</t>
-        </is>
-      </c>
-      <c r="X45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9247
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -6997,7 +6995,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5117
+          <t xml:space="preserve">3117
 </t>
         </is>
       </c>
@@ -7021,7 +7019,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -7033,7 +7031,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11226
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -7045,7 +7043,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -7063,7 +7061,8 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -7080,7 +7079,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -7116,7 +7115,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">837
+          <t xml:space="preserve">437
 </t>
         </is>
       </c>
@@ -644,7 +644,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">11242
 </t>
         </is>
       </c>
@@ -656,7 +656,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91124 1
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -674,19 +674,19 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 8 8
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1756
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
@@ -740,13 +740,13 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
@@ -767,7 +767,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>621</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -796,13 +796,23 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">191
@@ -827,7 +837,12 @@
 </t>
         </is>
       </c>
-      <c r="P5" s="2" t="n"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">205
@@ -842,7 +857,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
@@ -854,7 +869,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -902,8 +917,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4326
-</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -920,7 +934,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
@@ -938,19 +952,19 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">096
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">1006
 </t>
         </is>
       </c>
@@ -1010,7 +1024,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -1068,12 +1082,7 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">250
@@ -1088,13 +1097,13 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -1106,31 +1115,31 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">8726
 </t>
         </is>
       </c>
@@ -1142,7 +1151,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1160,7 +1169,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">1521
 </t>
         </is>
       </c>
@@ -1176,22 +1185,27 @@
 </t>
         </is>
       </c>
-      <c r="W7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7279
+          <t xml:space="preserve">779
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -1209,20 +1223,19 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297 6
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">2326
 </t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1233,7 +1246,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
@@ -1269,7 +1282,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1317,7 +1330,7 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1335,17 +1348,22 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1752
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">270
 </t>
         </is>
       </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="n"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1366,25 +1384,25 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1526
+          <t xml:space="preserve">8526
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">8225
 </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1396,7 +1414,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -1408,7 +1426,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
@@ -1450,13 +1468,13 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
+          <t xml:space="preserve">16173
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12319
+          <t xml:space="preserve">1319
 </t>
         </is>
       </c>
@@ -1486,19 +1504,19 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1295
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141024
+          <t xml:space="preserve">4024
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1546,18 +1564,28 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n"/>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -1572,7 +1600,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2193
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -1596,7 +1624,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
@@ -1662,7 +1690,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24451
+          <t xml:space="preserve">445
 </t>
         </is>
       </c>
@@ -1680,19 +1708,19 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -1704,13 +1732,13 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1728,68 +1756,66 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
+</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>8501</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">879
-</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25 8
-</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
-</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">850
-</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">587
-</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247 16
-</t>
-        </is>
-      </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1818,12 +1844,13 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t xml:space="preserve">383
+</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
@@ -1847,7 +1874,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1865,7 +1892,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1895,7 +1922,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -1943,13 +1970,13 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">1304
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
+          <t xml:space="preserve">11977
 </t>
         </is>
       </c>
@@ -1968,7 +1995,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
@@ -1986,7 +2013,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2355
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -2044,7 +2071,12 @@
 </t>
         </is>
       </c>
-      <c r="P13" s="2" t="n"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">286
@@ -2101,7 +2133,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2119,7 +2151,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
@@ -2149,7 +2181,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2159,7 +2191,12 @@
 </t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">57
@@ -2174,7 +2211,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -2192,7 +2229,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2222,7 +2259,7 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -2240,14 +2277,13 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2270,7 +2306,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">433
+          <t xml:space="preserve">1433
 </t>
         </is>
       </c>
@@ -2282,7 +2318,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2028
 </t>
         </is>
       </c>
@@ -2300,7 +2336,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -2318,7 +2354,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 8
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2330,7 +2366,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
@@ -2378,13 +2414,13 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
@@ -2396,7 +2432,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -2408,7 +2444,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -2426,13 +2462,13 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1992
+          <t xml:space="preserve">19928
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192499
+          <t xml:space="preserve">1499
 </t>
         </is>
       </c>
@@ -2450,54 +2486,48 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9246
+          <t xml:space="preserve">1946
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1058
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4448
+          <t xml:space="preserve">4441
 </t>
         </is>
       </c>
@@ -2515,13 +2545,13 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425
+          <t xml:space="preserve">10425
 </t>
         </is>
       </c>
@@ -2551,8 +2581,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2581,7 +2610,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">3998
 </t>
         </is>
       </c>
@@ -2605,31 +2634,38 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1115515
+</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">1202
+</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2646,7 +2682,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2664,19 +2700,19 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282240
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">1737
 </t>
         </is>
       </c>
@@ -2694,7 +2730,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2730,13 +2766,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -2748,7 +2783,8 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2759,19 +2795,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2782,30 +2818,31 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -2829,7 +2866,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">631
 </t>
         </is>
       </c>
@@ -2847,13 +2884,13 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2506
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -2883,7 +2920,8 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t xml:space="preserve">22234
+</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2924,13 +2962,13 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -2942,7 +2980,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
@@ -2966,7 +3004,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -3018,7 +3056,11 @@
 </t>
         </is>
       </c>
-      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>12</t>
@@ -3033,8 +3075,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9568
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3057,7 +3098,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -3073,10 +3114,16 @@
 </t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">244
+</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -3099,7 +3146,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -3111,13 +3158,13 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">12415
 </t>
         </is>
       </c>
@@ -3129,13 +3176,13 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7072
+          <t xml:space="preserve">707
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95 1
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -3147,7 +3194,8 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t xml:space="preserve">205
+</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -3236,22 +3284,22 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">867
@@ -3260,7 +3308,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3284,13 +3332,13 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3314,7 +3362,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8508
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -3338,37 +3386,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3741
+          <t xml:space="preserve">23746
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">2318
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">12475
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -3397,7 +3445,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
@@ -3439,7 +3487,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
+          <t xml:space="preserve">2564
 </t>
         </is>
       </c>
@@ -3451,7 +3499,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
@@ -3493,13 +3541,13 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19255
+          <t xml:space="preserve">1925
 </t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
@@ -3517,7 +3565,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6059
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
@@ -3535,13 +3583,13 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4953
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
@@ -3577,61 +3625,60 @@
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1462
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11431
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2952
+          <t xml:space="preserve">28952
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2267
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14110
+          <t xml:space="preserve">4110
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -3649,7 +3696,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">13985
 </t>
         </is>
       </c>
@@ -3661,25 +3708,25 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
@@ -3715,7 +3762,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -3733,7 +3780,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -3745,7 +3792,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 8
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -3757,7 +3804,7 @@
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -3779,7 +3826,12 @@
 </t>
         </is>
       </c>
-      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">54
@@ -3800,25 +3852,25 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">23740
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
@@ -3836,8 +3888,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3848,7 +3899,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3872,31 +3923,31 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 5
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -3908,7 +3959,7 @@
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -3926,7 +3977,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -3938,7 +3989,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -3956,7 +4007,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3292
+          <t xml:space="preserve">3298
 </t>
         </is>
       </c>
@@ -3968,7 +4019,8 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3985,7 +4037,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -3997,7 +4049,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4021,7 +4073,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89 2
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -4051,28 +4103,28 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">242
 </t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">218
@@ -4081,11 +4133,16 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1246
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">176
@@ -4106,13 +4163,13 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3548
+          <t xml:space="preserve">13544
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -4135,13 +4192,13 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4177,7 +4234,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -4213,13 +4270,14 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t xml:space="preserve">232
+</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -4236,8 +4294,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -4260,7 +4317,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">3893
 </t>
         </is>
       </c>
@@ -4308,7 +4365,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -4368,19 +4425,20 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
@@ -4397,8 +4455,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4421,12 +4478,14 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -4437,7 +4496,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -4449,7 +4508,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4461,7 +4520,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4479,7 +4538,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -4491,7 +4550,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4509,13 +4568,13 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
@@ -4527,7 +4586,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
@@ -4569,20 +4628,19 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118564
+          <t xml:space="preserve">18564
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1505
+          <t xml:space="preserve">1503
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4593,13 +4651,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">1525
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">1917
 </t>
         </is>
       </c>
@@ -4623,7 +4681,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9296
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4635,7 +4693,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
+          <t xml:space="preserve">1032
 </t>
         </is>
       </c>
@@ -4653,7 +4711,7 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
@@ -4677,7 +4735,7 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4695,12 +4753,14 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">1243
+</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t xml:space="preserve">3998
+</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4723,23 +4783,25 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">371
+</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>096</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4757,17 +4819,22 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -4812,13 +4879,13 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -4842,17 +4909,22 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="2" t="n"/>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4867,13 +4939,13 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437
+          <t xml:space="preserve">457
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4128
+          <t xml:space="preserve">13528
 </t>
         </is>
       </c>
@@ -4885,13 +4957,13 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1669
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1126
 </t>
         </is>
       </c>
@@ -4903,7 +4975,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -4915,7 +4987,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4933,7 +5005,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -4945,8 +5017,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4975,19 +5046,19 @@
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">1237
 </t>
         </is>
       </c>
@@ -4999,13 +5070,13 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5023,12 +5094,13 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t xml:space="preserve">3979
+</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">337
 </t>
         </is>
       </c>
@@ -5063,12 +5135,13 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5110,7 +5183,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2389
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5122,43 +5195,43 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">477
+          <t xml:space="preserve">1477
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">258
 </t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17276
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -5176,7 +5249,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
+          <t xml:space="preserve">13624
 </t>
         </is>
       </c>
@@ -5206,7 +5279,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5218,13 +5291,13 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5290,7 +5363,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -5308,7 +5381,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -5362,7 +5435,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -5386,7 +5459,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5398,7 +5471,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5440,13 +5513,13 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -5494,13 +5567,14 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -5517,7 +5591,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 0 1
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -5529,13 +5603,13 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 8
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5553,7 +5627,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -5601,7 +5675,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -5613,7 +5687,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5623,7 +5697,11 @@
 </t>
         </is>
       </c>
-      <c r="Z36" s="2" t="n"/>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -5638,7 +5716,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116835
+          <t xml:space="preserve">1683
 </t>
         </is>
       </c>
@@ -5650,19 +5728,19 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">002
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">1492
 </t>
         </is>
       </c>
@@ -5686,7 +5764,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1028
 </t>
         </is>
       </c>
@@ -5704,7 +5782,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
@@ -5734,7 +5812,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12560
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
@@ -5794,7 +5872,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3367
+          <t xml:space="preserve">23267
 </t>
         </is>
       </c>
@@ -5812,7 +5890,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">1251
 </t>
         </is>
       </c>
@@ -5836,7 +5914,8 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -5853,13 +5932,13 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 3
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -5889,7 +5968,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -5901,7 +5980,7 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -5913,7 +5992,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224 1
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -5931,7 +6010,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -5949,7 +6028,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008
+          <t xml:space="preserve">14008
 </t>
         </is>
       </c>
@@ -5973,17 +6052,22 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1585
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1821
-</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">139
@@ -6010,7 +6094,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2884
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -6022,13 +6106,13 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -6040,7 +6124,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -6064,7 +6148,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
@@ -6106,30 +6190,31 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">2841
+</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">11290
 </t>
         </is>
       </c>
@@ -6165,7 +6250,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -6213,13 +6298,13 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2083
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6231,11 +6316,16 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
-</t>
-        </is>
-      </c>
-      <c r="Z40" s="2" t="n"/>
+          <t xml:space="preserve">855
+</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">813
+</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>27</t>
@@ -6250,24 +6340,25 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
+          <t xml:space="preserve">2448
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
@@ -6285,7 +6376,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -6375,7 +6466,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -6387,7 +6478,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -6405,7 +6496,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14645
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
@@ -6429,7 +6520,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -6459,7 +6550,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6483,7 +6574,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -6501,13 +6592,13 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">1500
 </t>
         </is>
       </c>
@@ -6525,23 +6616,28 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="n"/>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -6556,7 +6652,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">341
+          <t xml:space="preserve">23413
 </t>
         </is>
       </c>
@@ -6568,7 +6664,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
@@ -6580,7 +6676,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -6622,19 +6718,19 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">1881
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -6652,7 +6748,7 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
@@ -6664,7 +6760,7 @@
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6682,12 +6778,12 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -6729,7 +6825,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -6753,7 +6849,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -6765,30 +6861,31 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">2041
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -6811,23 +6908,28 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
       <c r="X44" s="2" t="n"/>
       <c r="Y44" s="2" t="n"/>
       <c r="Z44" s="2" t="n"/>
@@ -6845,42 +6947,42 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1682111
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8251
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t xml:space="preserve">1056
+</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1833
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -6892,27 +6994,31 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19104
-</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n"/>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1092
+</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100921059
+          <t xml:space="preserve">12181
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0342
-</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6923,55 +7029,50 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575
+          <t xml:space="preserve">1575
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13820
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840
+          <t xml:space="preserve">4240
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">11215
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1455
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822
-</t>
-        </is>
-      </c>
-      <c r="X45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2312
+</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">483904
 </t>
         </is>
       </c>
@@ -7007,7 +7108,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -7019,13 +7120,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1041
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">11676
 </t>
         </is>
       </c>
@@ -7041,12 +7142,7 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -7067,7 +7163,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -7079,7 +7175,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -7115,11 +7211,16 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="n"/>
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1247
+</t>
+        </is>
+      </c>
       <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
@@ -626,128 +626,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">637
-</t>
+          <t>637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X4" s="2" t="n"/>
@@ -772,135 +751,113 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
-</t>
+          <t>741</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -922,140 +879,117 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1006
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
-</t>
+          <t>886</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
-</t>
+          <t>619</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1072,141 +1006,118 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8726
-</t>
+          <t>876</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">779
-</t>
+          <t>779</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1223,14 +1134,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1240,128 +1149,107 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
-</t>
+          <t>877</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1752
-</t>
+          <t>752</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1378,146 +1266,122 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
-</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8526
-</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225
-</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
+          <t>963</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4409
-</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16173
-</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
-</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
-</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
-</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4024
-</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,146 +1398,122 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,104 +1530,87 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">445
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>879</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1797,20 +1620,17 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -1820,14 +1640,12 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1844,140 +1662,117 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">383
-</t>
+          <t>383</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11977
-</t>
+          <t>977</t>
         </is>
       </c>
       <c r="Z12" s="2" t="n"/>
@@ -1995,146 +1790,122 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2151,134 +1922,112 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">509
-</t>
+          <t>509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2288,8 +2037,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2306,146 +2054,122 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1433
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
-</t>
+          <t>638</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2462,26 +2186,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19928
-</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
-</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
-</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2491,20 +2211,17 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -2515,68 +2232,57 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4441
-</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10425
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3687
-</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>531</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2586,14 +2292,12 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551
-</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2610,146 +2314,122 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
-</t>
+          <t>398</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115515
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
-</t>
+          <t>737</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2771,38 +2451,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2812,98 +2486,82 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2920,140 +2578,117 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22234
-</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -3080,140 +2715,117 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12415
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3230,146 +2842,122 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">433
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
+          <t>867</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3386,32 +2974,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23746
-</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12475
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3421,110 +3004,92 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3541,110 +3106,92 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925
-</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4372
-</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28952
-</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3654,32 +3201,27 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3696,146 +3238,122 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13985
-</t>
+          <t>385</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3852,38 +3370,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23740
-</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3893,104 +3405,87 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1748
-</t>
+          <t>748</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4007,146 +3502,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
-</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4163,8 +3634,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13544
-</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -4174,122 +3644,102 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -4299,8 +3749,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4317,140 +3766,117 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3893
-</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
-</t>
+          <t>649</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -4472,146 +3898,122 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>626</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4628,14 +4030,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18564
-</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1503
-</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4645,128 +4045,107 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1525
-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
-</t>
+          <t>917</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
-</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419
-</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
-</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3328
-</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
-</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4783,146 +4162,122 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
-</t>
+          <t>371</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>666</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4939,80 +4294,67 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">457
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13528
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1669
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -5022,62 +4364,52 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
-</t>
+          <t>566</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5094,38 +4426,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3979
-</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
-</t>
+          <t>337</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -5135,104 +4461,87 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477
-</t>
+          <t>477</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>776</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5249,146 +4558,122 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13624
-</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
-</t>
+          <t>873</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
-</t>
+          <t>786</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5405,146 +4690,122 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>879</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5561,140 +4822,117 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3989
-</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>723</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">782
-</t>
+          <t>782</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -5716,146 +4954,122 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
-</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
-</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
-</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1035
-</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
-</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1396
-</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3437
-</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">657
-</t>
+          <t>657</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
-</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3966
-</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5872,146 +5086,122 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23267
-</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
-</t>
+          <t>687</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
-</t>
+          <t>793</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -6028,146 +5218,122 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
-</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>545</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
-</t>
+          <t>784</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6184,146 +5350,122 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
-</t>
+          <t>744</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2841
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11290
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
-</t>
+          <t>813</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6340,146 +5482,122 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448
-</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
-</t>
+          <t>584</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6496,146 +5614,122 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6652,128 +5746,107 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23413
-</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>814</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
@@ -6783,14 +5856,12 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6807,74 +5878,62 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
-</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2041
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -6884,50 +5943,42 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X44" s="2" t="n"/>
@@ -6952,68 +6003,57 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
-</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
-</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1092
-</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12181
-</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -7023,63 +6063,53 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575
-</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
-</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
-</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4240
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11215
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455
-</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
-</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">483904
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -7096,129 +6126,112 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11676
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="Y46" s="2" t="n"/>

--- a/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
@@ -1271,7 +1271,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>442</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>222</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>328</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>310</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3263,34 +3263,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>193</t>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>408</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>913</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>181</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -5482,17 +5482,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>574</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>282</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -6104,7 +6104,7 @@
       <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">

--- a/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Top_Excel_with_OCR_Results.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>919</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>649</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>691</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>398</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>222</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>584</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>464</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -6104,7 +6104,7 @@
       <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -6136,49 +6136,49 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>202</t>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
